--- a/data/trans_orig/IP11B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11B-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11967</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,78%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36636</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61619</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>24113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33341</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -6565,12 +6565,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -7473,12 +7473,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27854</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>94970</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -11793,12 +11793,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12490,12 +12490,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34277</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13665,12 +13665,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15092,12 +15092,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15107,12 +15107,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15127,12 +15127,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15142,12 +15142,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15170,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15185,12 +15185,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -16000,12 +16000,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16015,12 +16015,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16035,12 +16035,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -16534,12 +16534,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16604,12 +16604,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16619,12 +16619,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16682,12 +16682,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16775,12 +16775,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16908,12 +16908,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16943,12 +16943,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
